--- a/exports/trend_1d/CHOLAFIN_full_report.xlsx
+++ b/exports/trend_1d/CHOLAFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.11</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42228</v>
+        <v>42229</v>
       </c>
       <c r="H2" t="n">
-        <v>128.95</v>
+        <v>125.55</v>
       </c>
       <c r="I2" t="n">
         <v>125.5560468404913</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K2" t="n">
-        <v>22.34</v>
+        <v>19.12</v>
       </c>
       <c r="L2" t="n">
         <v>5.65</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>8</v>
+      </c>
+      <c r="U2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>13.27</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42403</v>
+        <v>42404</v>
       </c>
       <c r="H3" t="n">
-        <v>130.75</v>
+        <v>134.5</v>
       </c>
       <c r="I3" t="n">
         <v>131.8411858314966</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.14</v>
+        <v>-7.13</v>
       </c>
       <c r="L3" t="n">
         <v>13.1</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42243</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="4">
@@ -648,25 +695,25 @@
         <v>13.21</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42682</v>
+        <v>42683</v>
       </c>
       <c r="H4" t="n">
-        <v>221.65</v>
+        <v>210.05</v>
       </c>
       <c r="I4" t="n">
         <v>217.9116657330734</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K4" t="n">
-        <v>64.8</v>
+        <v>56.17</v>
       </c>
       <c r="L4" t="n">
         <v>7.06</v>
       </c>
       <c r="M4" t="n">
-        <v>3.37</v>
+        <v>5.26</v>
       </c>
       <c r="N4" t="n">
         <v>5.79</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>186</v>
+        <v>187</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>10</v>
+      </c>
+      <c r="U4" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.23</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42732</v>
+        <v>42733</v>
       </c>
       <c r="H5" t="n">
-        <v>187.85</v>
+        <v>197.65</v>
       </c>
       <c r="I5" t="n">
         <v>192.3828483758193</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K5" t="n">
-        <v>10.57</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
         <v>2.83</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>17.3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42800</v>
+        <v>42801</v>
       </c>
       <c r="H6" t="n">
-        <v>190.85</v>
+        <v>186.8</v>
       </c>
       <c r="I6" t="n">
         <v>188.8992003703678</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.44</v>
+        <v>-5.49</v>
       </c>
       <c r="L6" t="n">
         <v>6.65</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>9.07</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42832</v>
+        <v>42835</v>
       </c>
       <c r="H7" t="n">
-        <v>200.9</v>
+        <v>210.6</v>
       </c>
       <c r="I7" t="n">
         <v>201.3854896927892</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.55</v>
+        <v>-12.74</v>
       </c>
       <c r="L7" t="n">
-        <v>9.31</v>
+        <v>14.99</v>
       </c>
       <c r="M7" t="n">
         <v>2.27</v>
       </c>
       <c r="N7" t="n">
-        <v>4.21</v>
+        <v>4.83</v>
       </c>
       <c r="O7" t="n">
         <v>-2.12</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>11</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42879</v>
+        <v>42880</v>
       </c>
       <c r="H8" t="n">
-        <v>201.75</v>
+        <v>198.5</v>
       </c>
       <c r="I8" t="n">
         <v>201.2113605538527</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.2</v>
+        <v>-5.75</v>
       </c>
       <c r="L8" t="n">
-        <v>5.15</v>
+        <v>6.43</v>
       </c>
       <c r="M8" t="n">
         <v>1.23</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>11.15</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42900</v>
+        <v>42901</v>
       </c>
       <c r="H9" t="n">
-        <v>218.8</v>
+        <v>222.85</v>
       </c>
       <c r="I9" t="n">
         <v>220.634772685149</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K9" t="n">
-        <v>-10.23</v>
+        <v>-12.27</v>
       </c>
       <c r="L9" t="n">
-        <v>11.94</v>
+        <v>13.85</v>
       </c>
       <c r="M9" t="n">
         <v>1.37</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43000</v>
+        <v>43003</v>
       </c>
       <c r="H10" t="n">
-        <v>227.65</v>
+        <v>219.35</v>
       </c>
       <c r="I10" t="n">
         <v>219.5628107401358</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="K10" t="n">
-        <v>2.15</v>
+        <v>-1.57</v>
       </c>
       <c r="L10" t="n">
         <v>5.74</v>
@@ -1011,7 +1130,7 @@
         <v>2.93</v>
       </c>
       <c r="N10" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.85</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>10.15</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43031</v>
+        <v>43032</v>
       </c>
       <c r="H11" t="n">
-        <v>228.3</v>
+        <v>235.4</v>
       </c>
       <c r="I11" t="n">
         <v>235.1695791944078</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.08</v>
+        <v>-7.32</v>
       </c>
       <c r="L11" t="n">
-        <v>5.95</v>
+        <v>7.96</v>
       </c>
       <c r="M11" t="n">
         <v>1.09</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.619999999999999</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43231</v>
+        <v>43234</v>
       </c>
       <c r="H12" t="n">
-        <v>317.8</v>
+        <v>314.8</v>
       </c>
       <c r="I12" t="n">
         <v>315.0218562166884</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>33.73</v>
       </c>
       <c r="L12" t="n">
         <v>8.539999999999999</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8</v>
+      </c>
+      <c r="U12" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>11.5</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43404</v>
+        <v>43405</v>
       </c>
       <c r="H13" t="n">
-        <v>254.1</v>
+        <v>267.8</v>
       </c>
       <c r="I13" t="n">
         <v>259.8977627887781</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K13" t="n">
-        <v>19.28</v>
+        <v>14.93</v>
       </c>
       <c r="L13" t="n">
         <v>4.83</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>117</v>
+        <v>118</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>19.59</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43486</v>
+        <v>43487</v>
       </c>
       <c r="H14" t="n">
-        <v>234.1</v>
+        <v>227.85</v>
       </c>
       <c r="I14" t="n">
         <v>233.0281814679648</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.58</v>
+        <v>-14.92</v>
       </c>
       <c r="L14" t="n">
-        <v>13.97</v>
+        <v>15.96</v>
       </c>
       <c r="M14" t="n">
         <v>2.63</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43496</v>
+        <v>43497</v>
       </c>
       <c r="H15" t="n">
-        <v>234.45</v>
+        <v>243.25</v>
       </c>
       <c r="I15" t="n">
         <v>243.228464386392</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.9</v>
+        <v>-6.76</v>
       </c>
       <c r="L15" t="n">
-        <v>3.69</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>2.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
         <v>-2.67</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>10.56</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43585</v>
+        <v>43587</v>
       </c>
       <c r="H16" t="n">
-        <v>277.75</v>
+        <v>267.75</v>
       </c>
       <c r="I16" t="n">
         <v>274.2362927819087</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K16" t="n">
-        <v>14.18</v>
+        <v>10.07</v>
       </c>
       <c r="L16" t="n">
         <v>6.82</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>4</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>11.86</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H17" t="n">
-        <v>270.15</v>
+        <v>285.5</v>
       </c>
       <c r="I17" t="n">
         <v>282.3608809244307</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9</v>
+        <v>-6.63</v>
       </c>
       <c r="L17" t="n">
-        <v>3.81</v>
+        <v>10.46</v>
       </c>
       <c r="M17" t="n">
-        <v>0.43</v>
+        <v>5.5</v>
       </c>
       <c r="N17" t="n">
-        <v>3.9</v>
+        <v>5.68</v>
       </c>
       <c r="O17" t="n">
         <v>-3.6</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>12</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43637</v>
+        <v>43640</v>
       </c>
       <c r="H18" t="n">
-        <v>275.6</v>
+        <v>274.7</v>
       </c>
       <c r="I18" t="n">
         <v>275.5862784402957</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K18" t="n">
-        <v>-3.47</v>
+        <v>-3.78</v>
       </c>
       <c r="L18" t="n">
         <v>5.2</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>12</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43717</v>
+        <v>43719</v>
       </c>
       <c r="H19" t="n">
-        <v>272.8</v>
+        <v>275.95</v>
       </c>
       <c r="I19" t="n">
         <v>274.1015046415886</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.46</v>
       </c>
       <c r="L19" t="n">
         <v>7.35</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.83</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43753</v>
+        <v>43754</v>
       </c>
       <c r="H20" t="n">
-        <v>279.85</v>
+        <v>270.6</v>
       </c>
       <c r="I20" t="n">
         <v>272.9697434623125</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K20" t="n">
-        <v>1.41</v>
+        <v>-1.94</v>
       </c>
       <c r="L20" t="n">
         <v>6.12</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>15.97</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43770</v>
+        <v>43773</v>
       </c>
       <c r="H21" t="n">
-        <v>313.2</v>
+        <v>316</v>
       </c>
       <c r="I21" t="n">
         <v>313.8078138498231</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K21" t="n">
-        <v>-15.74</v>
+        <v>-16.78</v>
       </c>
       <c r="L21" t="n">
-        <v>16.61</v>
+        <v>20.1</v>
       </c>
       <c r="M21" t="n">
         <v>0.73</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>10.77</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43833</v>
+        <v>43836</v>
       </c>
       <c r="H22" t="n">
-        <v>303.05</v>
+        <v>291.5</v>
       </c>
       <c r="I22" t="n">
         <v>293.3753120717373</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.1</v>
+        <v>-7.75</v>
       </c>
       <c r="L22" t="n">
-        <v>7.33</v>
+        <v>9.16</v>
       </c>
       <c r="M22" t="n">
-        <v>0.73</v>
+        <v>3.81</v>
       </c>
       <c r="N22" t="n">
         <v>4.49</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>9.25</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43840</v>
+        <v>43843</v>
       </c>
       <c r="H23" t="n">
-        <v>314.1</v>
+        <v>319.95</v>
       </c>
       <c r="I23" t="n">
         <v>316.8032834313846</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K23" t="n">
-        <v>-7.75</v>
+        <v>-9.76</v>
       </c>
       <c r="L23" t="n">
-        <v>8.4</v>
+        <v>10.02</v>
       </c>
       <c r="M23" t="n">
         <v>1.34</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,25 +2075,25 @@
         <v>9.09</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H24" t="n">
-        <v>314.55</v>
+        <v>306.5</v>
       </c>
       <c r="I24" t="n">
         <v>307.7460500672137</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.69</v>
+        <v>-4.2</v>
       </c>
       <c r="L24" t="n">
-        <v>3.44</v>
+        <v>6.06</v>
       </c>
       <c r="M24" t="n">
-        <v>1.13</v>
+        <v>1.89</v>
       </c>
       <c r="N24" t="n">
         <v>2.75</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.11</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43998</v>
+        <v>43999</v>
       </c>
       <c r="H25" t="n">
-        <v>155.45</v>
+        <v>168.2</v>
       </c>
       <c r="I25" t="n">
         <v>162.6889879413341</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K25" t="n">
-        <v>49.28</v>
+        <v>45.12</v>
       </c>
       <c r="L25" t="n">
         <v>3.43</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>26.86</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44376</v>
+        <v>44377</v>
       </c>
       <c r="H26" t="n">
-        <v>519.35</v>
+        <v>513.25</v>
       </c>
       <c r="I26" t="n">
         <v>515.7015923730928</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K26" t="n">
-        <v>208.77</v>
+        <v>205.14</v>
       </c>
       <c r="L26" t="n">
         <v>8.92</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>260</v>
+        <v>261</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>14</v>
+      </c>
+      <c r="U26" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>10.04</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44407</v>
+        <v>44410</v>
       </c>
       <c r="H27" t="n">
-        <v>475.75</v>
+        <v>526.45</v>
       </c>
       <c r="I27" t="n">
         <v>520.9548912496878</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>7.31</v>
+        <v>-2.57</v>
       </c>
       <c r="L27" t="n">
         <v>3.8</v>
@@ -1980,7 +2303,7 @@
         <v>1.8</v>
       </c>
       <c r="N27" t="n">
-        <v>1.74</v>
+        <v>10.66</v>
       </c>
       <c r="O27" t="n">
         <v>-1.17</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>16.22</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44525</v>
+        <v>44526</v>
       </c>
       <c r="H28" t="n">
-        <v>584.35</v>
+        <v>544.8</v>
       </c>
       <c r="I28" t="n">
         <v>572.2089987931752</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K28" t="n">
-        <v>11</v>
+        <v>3.49</v>
       </c>
       <c r="L28" t="n">
         <v>10.72</v>
@@ -2037,7 +2372,7 @@
         <v>1.68</v>
       </c>
       <c r="N28" t="n">
-        <v>4.27</v>
+        <v>6.77</v>
       </c>
       <c r="O28" t="n">
         <v>10.66</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>17.82</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44565</v>
+        <v>44566</v>
       </c>
       <c r="H29" t="n">
-        <v>546.05</v>
+        <v>568</v>
       </c>
       <c r="I29" t="n">
         <v>556.9759533190145</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.23</v>
+        <v>-4.26</v>
       </c>
       <c r="L29" t="n">
         <v>8.109999999999999</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>12.69</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44624</v>
+        <v>44627</v>
       </c>
       <c r="H30" t="n">
-        <v>658.5</v>
+        <v>607.3</v>
       </c>
       <c r="I30" t="n">
         <v>613.3868697051894</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K30" t="n">
-        <v>15.93</v>
+        <v>6.92</v>
       </c>
       <c r="L30" t="n">
         <v>4.53</v>
@@ -2151,7 +2510,7 @@
         <v>3.11</v>
       </c>
       <c r="N30" t="n">
-        <v>5.33</v>
+        <v>7.78</v>
       </c>
       <c r="O30" t="n">
         <v>4.02</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>18.2</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44636</v>
+        <v>44637</v>
       </c>
       <c r="H31" t="n">
-        <v>697.4</v>
+        <v>719.85</v>
       </c>
       <c r="I31" t="n">
         <v>702.4816502866237</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>-14.84</v>
+        <v>-18.53</v>
       </c>
       <c r="L31" t="n">
-        <v>17.49</v>
+        <v>19.21</v>
       </c>
       <c r="M31" t="n">
-        <v>1.15</v>
+        <v>1.52</v>
       </c>
       <c r="N31" t="n">
         <v>4.68</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>12.65</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44686</v>
+        <v>44687</v>
       </c>
       <c r="H32" t="n">
-        <v>715.3</v>
+        <v>636.85</v>
       </c>
       <c r="I32" t="n">
         <v>672.5566985208714</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.63</v>
+        <v>-11.53</v>
       </c>
       <c r="L32" t="n">
-        <v>4.84</v>
+        <v>12.59</v>
       </c>
       <c r="M32" t="n">
-        <v>2.07</v>
+        <v>2.68</v>
       </c>
       <c r="N32" t="n">
-        <v>4.6</v>
+        <v>10.97</v>
       </c>
       <c r="O32" t="n">
         <v>3.22</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>19.78</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44762</v>
+        <v>44763</v>
       </c>
       <c r="H33" t="n">
-        <v>672.3</v>
+        <v>686</v>
       </c>
       <c r="I33" t="n">
         <v>685.2371711285632</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.57</v>
+        <v>-7.72</v>
       </c>
       <c r="L33" t="n">
         <v>12.62</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.98</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H34" t="n">
-        <v>784.1</v>
+        <v>738.5</v>
       </c>
       <c r="I34" t="n">
         <v>746.0116884425041</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K34" t="n">
-        <v>14.3</v>
+        <v>7.65</v>
       </c>
       <c r="L34" t="n">
         <v>2.77</v>
@@ -2379,7 +2786,7 @@
         <v>3.23</v>
       </c>
       <c r="N34" t="n">
-        <v>3.05</v>
+        <v>5.82</v>
       </c>
       <c r="O34" t="n">
         <v>2.04</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>12.57</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44957</v>
+        <v>44958</v>
       </c>
       <c r="H35" t="n">
-        <v>706.95</v>
+        <v>749.8</v>
       </c>
       <c r="I35" t="n">
         <v>730.431253589029</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K35" t="n">
-        <v>4.27</v>
+        <v>-1.53</v>
       </c>
       <c r="L35" t="n">
         <v>5.88</v>
       </c>
       <c r="M35" t="n">
-        <v>2.35</v>
+        <v>3.42</v>
       </c>
       <c r="N35" t="n">
-        <v>5.46</v>
+        <v>6.06</v>
       </c>
       <c r="O35" t="n">
         <v>-5.82</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>89</v>
+        <v>90</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>6</v>
+      </c>
+      <c r="U35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45008</v>
+        <v>45009</v>
       </c>
       <c r="H36" t="n">
-        <v>746.7</v>
+        <v>727.65</v>
       </c>
       <c r="I36" t="n">
         <v>730.5051579708236</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.41</v>
+        <v>-2.95</v>
       </c>
       <c r="L36" t="n">
-        <v>2.49</v>
+        <v>3.61</v>
       </c>
       <c r="M36" t="n">
         <v>0.88</v>
       </c>
       <c r="N36" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
         <v>6.06</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>8.07</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H37" t="n">
-        <v>761.3</v>
+        <v>778.6</v>
       </c>
       <c r="I37" t="n">
         <v>773.3644114966273</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.62</v>
+        <v>-7</v>
       </c>
       <c r="L37" t="n">
-        <v>5.01</v>
+        <v>7.3</v>
       </c>
       <c r="M37" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="N37" t="n">
         <v>2.28</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>7.86</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45139</v>
+        <v>45140</v>
       </c>
       <c r="H38" t="n">
-        <v>1130.45</v>
+        <v>1099.4</v>
       </c>
       <c r="I38" t="n">
         <v>1103.598153468027</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K38" t="n">
-        <v>45.19</v>
+        <v>41.2</v>
       </c>
       <c r="L38" t="n">
         <v>1.88</v>
       </c>
       <c r="M38" t="n">
-        <v>1.62</v>
+        <v>2.78</v>
       </c>
       <c r="N38" t="n">
         <v>3.01</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.41</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45163</v>
+        <v>45166</v>
       </c>
       <c r="H39" t="n">
-        <v>1082.2</v>
+        <v>1092.95</v>
       </c>
       <c r="I39" t="n">
         <v>1088.984481240716</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K39" t="n">
-        <v>1.56</v>
+        <v>0.59</v>
       </c>
       <c r="L39" t="n">
         <v>2.46</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.98</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45222</v>
+        <v>45224</v>
       </c>
       <c r="H40" t="n">
-        <v>1167.25</v>
+        <v>1147.05</v>
       </c>
       <c r="I40" t="n">
         <v>1158.952027828859</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="K40" t="n">
-        <v>6.8</v>
+        <v>4.95</v>
       </c>
       <c r="L40" t="n">
         <v>1.63</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>8.5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45273</v>
+        <v>45274</v>
       </c>
       <c r="H41" t="n">
-        <v>1180.6</v>
+        <v>1228.9</v>
       </c>
       <c r="I41" t="n">
         <v>1185.467787487693</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.92</v>
+        <v>-7.14</v>
       </c>
       <c r="L41" t="n">
-        <v>6.14</v>
+        <v>7.41</v>
       </c>
       <c r="M41" t="n">
         <v>1.4</v>
       </c>
       <c r="N41" t="n">
-        <v>2.96</v>
+        <v>4.09</v>
       </c>
       <c r="O41" t="n">
         <v>-1.73</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>8.57</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45321</v>
+        <v>45322</v>
       </c>
       <c r="H42" t="n">
-        <v>1214.05</v>
+        <v>1184.15</v>
       </c>
       <c r="I42" t="n">
         <v>1194.046924306429</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.21</v>
+        <v>-3.64</v>
       </c>
       <c r="L42" t="n">
-        <v>3.29</v>
+        <v>4.35</v>
       </c>
       <c r="M42" t="n">
         <v>2.3</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>3</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.04</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45378</v>
+        <v>45379</v>
       </c>
       <c r="H43" t="n">
-        <v>1130.2</v>
+        <v>1156.6</v>
       </c>
       <c r="I43" t="n">
         <v>1136.70934523096</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K43" t="n">
-        <v>4.56</v>
+        <v>2.33</v>
       </c>
       <c r="L43" t="n">
         <v>3.2</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>9.34</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45398</v>
+        <v>45400</v>
       </c>
       <c r="H44" t="n">
-        <v>1130</v>
+        <v>1118.8</v>
       </c>
       <c r="I44" t="n">
         <v>1123.630783047493</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.3</v>
+        <v>-3.27</v>
       </c>
       <c r="L44" t="n">
-        <v>2.63</v>
+        <v>3.61</v>
       </c>
       <c r="M44" t="n">
         <v>2.34</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>9.31</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45412</v>
+        <v>45414</v>
       </c>
       <c r="H45" t="n">
-        <v>1193.3</v>
+        <v>1301.6</v>
       </c>
       <c r="I45" t="n">
         <v>1209.890124893812</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.66</v>
+        <v>-16.34</v>
       </c>
       <c r="L45" t="n">
-        <v>8.4</v>
+        <v>17.07</v>
       </c>
       <c r="M45" t="n">
-        <v>0.96</v>
+        <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>2.23</v>
+        <v>9.08</v>
       </c>
       <c r="O45" t="n">
         <v>-0.99</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.29</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45516</v>
+        <v>45517</v>
       </c>
       <c r="H46" t="n">
-        <v>1348.75</v>
+        <v>1314.9</v>
       </c>
       <c r="I46" t="n">
         <v>1328.2132691823</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K46" t="n">
-        <v>3.62</v>
+        <v>1.02</v>
       </c>
       <c r="L46" t="n">
         <v>7.99</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>12.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45534</v>
+        <v>45537</v>
       </c>
       <c r="H47" t="n">
-        <v>1455.6</v>
+        <v>1486.3</v>
       </c>
       <c r="I47" t="n">
         <v>1468.648832607502</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>-10.7</v>
+        <v>-13.04</v>
       </c>
       <c r="L47" t="n">
-        <v>12.47</v>
+        <v>13.62</v>
       </c>
       <c r="M47" t="n">
         <v>0.76</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.56</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H48" t="n">
-        <v>1516.25</v>
+        <v>1497.4</v>
       </c>
       <c r="I48" t="n">
         <v>1514.633279215629</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K48" t="n">
-        <v>2.02</v>
+        <v>0.75</v>
       </c>
       <c r="L48" t="n">
         <v>2.27</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>9.119999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45635</v>
+        <v>45636</v>
       </c>
       <c r="H49" t="n">
-        <v>1282.25</v>
+        <v>1336.3</v>
       </c>
       <c r="I49" t="n">
         <v>1328.438271701233</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K49" t="n">
-        <v>14.37</v>
+        <v>10.76</v>
       </c>
       <c r="L49" t="n">
         <v>6.01</v>
@@ -3234,7 +3821,7 @@
         <v>3.61</v>
       </c>
       <c r="N49" t="n">
-        <v>3.55</v>
+        <v>4.22</v>
       </c>
       <c r="O49" t="n">
         <v>-1.24</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>10.37</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45644</v>
+        <v>45645</v>
       </c>
       <c r="H50" t="n">
-        <v>1242.75</v>
+        <v>1213.75</v>
       </c>
       <c r="I50" t="n">
         <v>1236.40103563513</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>-7</v>
+        <v>-9.17</v>
       </c>
       <c r="L50" t="n">
-        <v>7.75</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="M50" t="n">
-        <v>0.61</v>
+        <v>1.91</v>
       </c>
       <c r="N50" t="n">
         <v>3.03</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>9.48</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45659</v>
+        <v>45660</v>
       </c>
       <c r="H51" t="n">
-        <v>1271.5</v>
+        <v>1320.25</v>
       </c>
       <c r="I51" t="n">
         <v>1282.865181001731</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.76</v>
+        <v>-8.77</v>
       </c>
       <c r="L51" t="n">
-        <v>5.13</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="M51" t="n">
         <v>1.94</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>10.76</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45681</v>
+        <v>45684</v>
       </c>
       <c r="H52" t="n">
-        <v>1223.05</v>
+        <v>1175.35</v>
       </c>
       <c r="I52" t="n">
         <v>1187.205933049738</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>-7.36</v>
+        <v>-10.98</v>
       </c>
       <c r="L52" t="n">
-        <v>7.95</v>
+        <v>11.4</v>
       </c>
       <c r="M52" t="n">
         <v>2</v>
       </c>
       <c r="N52" t="n">
-        <v>2.59</v>
+        <v>3.9</v>
       </c>
       <c r="O52" t="n">
         <v>3.83</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>12.43</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45689</v>
+        <v>45691</v>
       </c>
       <c r="H53" t="n">
-        <v>1265.5</v>
+        <v>1337.65</v>
       </c>
       <c r="I53" t="n">
         <v>1321.41426386075</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K53" t="n">
-        <v>-7.67</v>
+        <v>-13.81</v>
       </c>
       <c r="L53" t="n">
-        <v>12.46</v>
+        <v>14.04</v>
       </c>
       <c r="M53" t="n">
         <v>2.52</v>
       </c>
       <c r="N53" t="n">
-        <v>5.65</v>
+        <v>5.7</v>
       </c>
       <c r="O53" t="n">
         <v>-3.9</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>17.03</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H54" t="n">
-        <v>1453.3</v>
+        <v>1386.1</v>
       </c>
       <c r="I54" t="n">
         <v>1403.784053118248</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K54" t="n">
-        <v>8.65</v>
+        <v>3.62</v>
       </c>
       <c r="L54" t="n">
         <v>7.37</v>
@@ -3519,7 +4166,7 @@
         <v>0.8</v>
       </c>
       <c r="N54" t="n">
-        <v>3.4</v>
+        <v>4.62</v>
       </c>
       <c r="O54" t="n">
         <v>5.7</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>11.58</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H55" t="n">
-        <v>1475.7</v>
+        <v>1560.3</v>
       </c>
       <c r="I55" t="n">
         <v>1546.597612699227</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K55" t="n">
-        <v>-6.46</v>
+        <v>-12.57</v>
       </c>
       <c r="L55" t="n">
-        <v>8.119999999999999</v>
+        <v>13.92</v>
       </c>
       <c r="M55" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="N55" t="n">
-        <v>5.57</v>
+        <v>5.73</v>
       </c>
       <c r="O55" t="n">
         <v>-4.62</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>13.47</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45811</v>
+        <v>45812</v>
       </c>
       <c r="H56" t="n">
-        <v>1566.3</v>
+        <v>1512.7</v>
       </c>
       <c r="I56" t="n">
         <v>1534.62580906794</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K56" t="n">
-        <v>0.38</v>
+        <v>-3.05</v>
       </c>
       <c r="L56" t="n">
         <v>6.07</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>9.83</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45814</v>
+        <v>45817</v>
       </c>
       <c r="H57" t="n">
-        <v>1593.2</v>
+        <v>1644.6</v>
       </c>
       <c r="I57" t="n">
         <v>1643.299228053125</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>-5.32</v>
+        <v>-8.720000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>7.34</v>
+        <v>9.27</v>
       </c>
       <c r="M57" t="n">
-        <v>0.61</v>
+        <v>1.68</v>
       </c>
       <c r="N57" t="n">
         <v>5.4</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.55</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45863</v>
+        <v>45866</v>
       </c>
       <c r="H58" t="n">
-        <v>1503.8</v>
+        <v>1490.3</v>
       </c>
       <c r="I58" t="n">
         <v>1503.013018611815</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K58" t="n">
-        <v>-8.56</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="L58" t="n">
         <v>10.88</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="H59" t="n">
-        <v>1517.7</v>
+        <v>1583.1</v>
       </c>
       <c r="I59" t="n">
         <v>1538.151866403831</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.84</v>
+        <v>-6.23</v>
       </c>
       <c r="L59" t="n">
-        <v>3.09</v>
+        <v>6.57</v>
       </c>
       <c r="M59" t="n">
         <v>2.63</v>
       </c>
       <c r="N59" t="n">
-        <v>4.18</v>
+        <v>4.31</v>
       </c>
       <c r="O59" t="n">
         <v>-0.9</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>3</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.83</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="H60" t="n">
-        <v>1648.1</v>
+        <v>1584.9</v>
       </c>
       <c r="I60" t="n">
         <v>1628.766344327186</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K60" t="n">
-        <v>4.11</v>
+        <v>0.11</v>
       </c>
       <c r="L60" t="n">
         <v>4.26</v>
@@ -3861,7 +4580,7 @@
         <v>1.23</v>
       </c>
       <c r="N60" t="n">
-        <v>3.58</v>
+        <v>3.83</v>
       </c>
       <c r="O60" t="n">
         <v>4.31</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>4</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>10.37</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46023</v>
+        <v>46024</v>
       </c>
       <c r="H61" t="n">
-        <v>1724</v>
+        <v>1781.1</v>
       </c>
       <c r="I61" t="n">
         <v>1749.239424961156</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K61" t="n">
-        <v>-8.779999999999999</v>
+        <v>-12.38</v>
       </c>
       <c r="L61" t="n">
-        <v>9</v>
+        <v>12.88</v>
       </c>
       <c r="M61" t="n">
         <v>1.27</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>9.289999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H62" t="n">
-        <v>1700.4</v>
+        <v>1649.9</v>
       </c>
       <c r="I62" t="n">
         <v>1667.195402368213</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K62" t="n">
-        <v>-4.53</v>
+        <v>-7.37</v>
       </c>
       <c r="L62" t="n">
-        <v>5.85</v>
+        <v>7.69</v>
       </c>
       <c r="M62" t="n">
         <v>0.65</v>
       </c>
       <c r="N62" t="n">
-        <v>2.1</v>
+        <v>2.97</v>
       </c>
       <c r="O62" t="n">
         <v>3.31</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>9.210000000000001</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H63" t="n">
-        <v>1694.4</v>
+        <v>1739.5</v>
       </c>
       <c r="I63" t="n">
         <v>1708.259152548236</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.7</v>
+        <v>-5.43</v>
       </c>
       <c r="L63" t="n">
-        <v>5.46</v>
+        <v>5.64</v>
       </c>
       <c r="M63" t="n">
         <v>5.99</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>12.35</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="H64" t="n">
-        <v>1626.3</v>
+        <v>1583</v>
       </c>
       <c r="I64" t="n">
         <v>1609.571627860043</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K64" t="n">
-        <v>-6.51</v>
+        <v>-9</v>
       </c>
       <c r="L64" t="n">
-        <v>6.87</v>
+        <v>15.78</v>
       </c>
       <c r="M64" t="n">
         <v>4.03</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>8.98</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H65" t="n">
-        <v>1415</v>
+        <v>1554.3</v>
       </c>
       <c r="I65" t="n">
         <v>1515.187182006171</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K65" t="n">
-        <v>10.61</v>
+        <v>1.81</v>
       </c>
       <c r="L65" t="n">
         <v>3.15</v>
       </c>
       <c r="M65" t="n">
-        <v>3.48</v>
+        <v>6.22</v>
       </c>
       <c r="N65" t="n">
-        <v>3.87</v>
+        <v>9.84</v>
       </c>
       <c r="O65" t="n">
         <v>-2.66</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>14.3</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H66" t="n">
-        <v>1546.3</v>
+        <v>1527.9</v>
       </c>
       <c r="I66" t="n">
         <v>1532.554822443458</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.51</v>
+        <v>-1.7</v>
       </c>
       <c r="L66" t="n">
         <v>5.28</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,25 +5042,25 @@
         <v>9.74</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="H67" t="n">
-        <v>1568.1</v>
+        <v>1653.6</v>
       </c>
       <c r="I67" t="n">
         <v>1606.913582048126</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>-2.63</v>
+        <v>-8.23</v>
       </c>
       <c r="L67" t="n">
-        <v>6.68</v>
+        <v>8.91</v>
       </c>
       <c r="M67" t="n">
-        <v>2.37</v>
+        <v>2.67</v>
       </c>
       <c r="N67" t="n">
         <v>7.78</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>11.96</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H68" t="n">
-        <v>1728</v>
+        <v>1717.3</v>
       </c>
       <c r="I68" t="n">
         <v>1724.684875797767</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K68" t="n">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="L68" t="n">
         <v>2.8</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>7.43</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="H69" t="n">
-        <v>1773.8</v>
+        <v>1849.9</v>
       </c>
       <c r="I69" t="n">
         <v>1841.280770217428</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K69" t="n">
-        <v>-3.29</v>
+        <v>-7.72</v>
       </c>
       <c r="L69" t="n">
-        <v>7.12</v>
+        <v>8.49</v>
       </c>
       <c r="M69" t="n">
         <v>2.97</v>
       </c>
       <c r="N69" t="n">
-        <v>3.53</v>
+        <v>4.29</v>
       </c>
       <c r="O69" t="n">
         <v>-0.62</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>11.62</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="H70" t="n">
-        <v>1765.6</v>
+        <v>1764.5</v>
       </c>
       <c r="I70" t="n">
         <v>1764.62441293353</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.56</v>
+        <v>-4.62</v>
       </c>
       <c r="L70" t="n">
-        <v>5.06</v>
+        <v>5.53</v>
       </c>
       <c r="M70" t="n">
         <v>1.44</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>28</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9449,7 +10308,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>60</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="6">
@@ -9459,7 +10318,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7">
@@ -9469,7 +10328,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="8">
@@ -9479,7 +10338,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -9489,7 +10348,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -9499,7 +10358,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11">
@@ -9509,7 +10368,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -9519,7 +10378,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13">
@@ -9529,7 +10388,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37.7</v>
+        <v>34.8</v>
       </c>
     </row>
     <row r="14">
@@ -9539,7 +10398,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.4</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="15">
@@ -9549,7 +10408,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11.2</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="16">
@@ -9559,7 +10418,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.58</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="17">
@@ -9569,7 +10428,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>208.77</v>
+        <v>205.14</v>
       </c>
     </row>
     <row r="18">
@@ -9579,7 +10438,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>40.6</v>
+        <v>31.9</v>
       </c>
     </row>
     <row r="19">
@@ -9589,7 +10448,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.61</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="20">
@@ -9599,7 +10458,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.01</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="21">
@@ -9609,7 +10468,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17.49</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="22">
@@ -9619,7 +10478,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -9629,7 +10488,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24">
@@ -9639,7 +10498,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.08</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="25">
@@ -9659,7 +10518,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.59</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="27">
@@ -9679,7 +10538,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
